--- a/Result/checksun_type/清潔用品.xlsx
+++ b/Result/checksun_type/清潔用品.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>16.6</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>16.74</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>16.97</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>16.74</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>16.97</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>4837481.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>4898844.4</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>4898844.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>6522159.0</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>7467257.5</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>7467257.5</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-510468.3037822163</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>4837481</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>4837481.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>16.47</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>16.74</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>16.97</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>16.74</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>16.97</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>1318745.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>6868173.2</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>6868173.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>6493460.2</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>7528953.3</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>7528953.3</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-486853.7959417813</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>1318745</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>1318745.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>16.46</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>16.76</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>16.98</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>16.76</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>16.98</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>6158586.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>7942264.0</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>7942264</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>6735639.1</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>7598178.06</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>7598178.06</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-58723.72060038242</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>6158586</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>6158586.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>16.49</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>16.78</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>16.99</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>16.78</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>16.99</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>7947232.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>7489543.2</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>7489543.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>6958233.1</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>7762346.68</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>7762346.68</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>36433.55562305823</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>7947232</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>7947232.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>16.63</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>16.85</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>17.0</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>16.85</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>17</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>4232178.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>8620782.8</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>8620782.800000001</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>6890359.7</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>7694953.34</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>7694953.34</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-20569.31961570866</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>4232178</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>4232178.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>16.72</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>16.91</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>17.02</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>16.91</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>17.02</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>14684125.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>8145473.6</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>8145473.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>6803172.5</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>7656264.52</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>7656264.52</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>296774.1200294727</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>14684125</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>14684125.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>16.83</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>16.95</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>17.03</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>16.95</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>17.03</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>6689199.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>6118747.2</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>6118747.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>5574574.1</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>7444881.34</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>7444881.34</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-380328.6490498912</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>6689199</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>6689199.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>16.81</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>16.97</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>17.04</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>16.97</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>17.04</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>3894982.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>5529014.2</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>5529014.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>5491244.3</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>7354839.54</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>7354839.54</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-477435.9388400586</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>3894982</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>3894982.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>16.76</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>16.98</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>17.03</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>16.98</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>17.03</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>13603430.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>6426923.0</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>6426923</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>5411234.1</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>7385529.72</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>7385529.72</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>-299728.9621531535</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>13603430</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>13603430.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>16.7</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>16.98</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>17.03</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>16.98</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>17.03</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>1855632.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>5159936.6</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>5159936.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>4534923.5</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>7286760.8</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>7286760.8</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-1075348.103952104</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>1855632</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>1855632.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>16.72</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>16.98</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>17.03</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>16.98</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>17.03</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>4550493.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>5460871.4</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>5460871.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>4599369.5</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>7406016.88</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>7406016.88</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-886277.5170951728</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>4550493</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>4550493.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>34.27</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>32.35</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>32.64</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>32.35</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>32.64</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>30752.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>26021.8</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>26021.8</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>27135.3</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>14215.12</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>14215.12</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>1676.657039741152</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>30752</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>30752.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>33.98</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>32.19</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>32.61</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>32.19</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>32.61</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>15599.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>23408.4</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>23408.4</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>25268.3</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>14319.64</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>14319.64</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>1114.689186374952</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>15599</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>15599.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>33.77</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>32.07</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>32.62</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>32.07</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>32.62</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>9517.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>24723.6</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>24723.6</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>24634.6</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>14301.02</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>14301.02</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>1895.603353481278</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>9517</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>9517.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>33.68</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>31.99</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>32.64</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>31.99</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>32.64</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>31971.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>27396.0</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>27396</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>24460.1</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>14465.96</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>14465.96</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>3595.137758151694</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>31971</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>31971.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>33.58</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>31.91</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>32.67</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>31.91</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>32.67</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>42270.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>26727.6</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>26727.6</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>22014.3</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>14159.48</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>14159.48</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>3488.860559175446</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>42270</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>42270.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>33.34</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>31.81</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>32.67</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>31.81</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>32.67</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>17685.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>28248.8</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>28248.8</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>18790.2</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>13569.2</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>13569.2</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>2108.9695406674</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>17685</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>17685.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>32.92999999999999</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>31.75</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>32.7</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>31.75</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>32.7</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>22175.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>27128.2</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>27128.2</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>17701.2</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>13365.52</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>13365.52</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>2696.4834592035</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>22175</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>22175.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>32.44</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>31.71</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>32.72</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>31.71</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>32.72</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>22879.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>24545.6</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>24545.6</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>16522.3</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>13109.9</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>13109.9</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>2958.414647854945</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>22879</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>22879.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>31.82</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>31.66</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>32.74</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>31.66</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>32.74</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>28629.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>21524.2</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>21524.2</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>15788.2</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>12943.64</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>12943.64</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>3151.51582279076</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>28629</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>28629.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>31.32999999999999</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>31.61</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>32.78</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>31.61</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>32.78</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>49876.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>17301.0</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>17301</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>13897.0</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>12734.7</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>12734.7</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>2698.74907902797</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>49876</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>49876.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>30.82</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>31.55</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>32.8</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>31.55</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>32.8</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>12082.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>9331.6</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>9331.6</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>10294.0</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>11920.4</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>11920.4</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>-320.9087363127292</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>12082</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>12082.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>43.2</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>43.2</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>45.12</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>45.12</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>3383849.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>2709230.0</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>2709230</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>2380673.2</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>5209044.42</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>5209044.42</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>-29116.58208910562</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>3383849</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>3383849.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>42.84</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>43.3</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>45.22</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>45.22</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>3775435.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>2142386.0</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>2142386</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>2385309.8</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>5210679.64</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>5210679.64</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>-103339.04511018</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>3775435</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>3775435.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>42.52999999999999</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>43.45</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>45.36</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>43.45</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>45.36</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>3711041.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>1585357.8</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>1585357.8</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>2538671.3</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>5178587.7</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>5178587.7</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>-247636.0978149222</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>3711041</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>3711041.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>42.4</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>43.63</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>45.49</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>43.63</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>45.49</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>937215.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>1363163.2</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>1363163.2</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>2470234.2</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>5145449.24</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>5145449.24</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>-438031.241042593</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>937215</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>937215.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>42.77</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>43.86</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>45.64</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>43.86</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>45.64</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>1738610.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>2232151.8</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>2232151.8</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>2531162.0</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>5179004.82</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>5179004.82</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>-397184.6870448873</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>1738610</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>1738610.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>42.82</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>44.02</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>45.8</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>44.02</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>45.8</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>549629.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>2052116.4</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>2052116.4</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>2595180.8</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>5266456.46</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>5266456.46</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>-410511.0496537043</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>549629</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>549629.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>43.13</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>44.15</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>45.95</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>44.15</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>45.95</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>990294.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>2628233.6</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>2628233.6</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>2769274.0</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>5285586.92</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>5285586.92</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>-287496.7801786675</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>990294</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>990294.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>43.39</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>44.3</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>46.11</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>44.3</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>46.11</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>2600068.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>3491984.8</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>3491984.8</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>2750464.3</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>5284330.0</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>5284330</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>-148708.4744936624</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>2600068</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>2600068.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>43.36</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>44.48</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>46.25</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>44.48</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>46.25</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>5282158.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>3577305.2</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>3577305.2</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>2611522.3</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>5283426.94</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>5283426.94</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>-117604.2351403106</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>5282158</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>5282158.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>42.98</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>44.61</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>46.35</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>44.61</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>46.35</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>838433.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>2830172.2</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>2830172.2</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>2518129.9</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>5219863.88</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>5219863.88</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>-356336.2419519396</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>838433</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>838433.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>42.95</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>44.81</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>46.5</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>44.81</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>46.5</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>3430215.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>3138245.2</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>3138245.2</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>2526129.4</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>5240025.44</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>5240025.44</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>-208542.2787559833</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>3430215</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>3430215.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>28.73</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>28.54</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>28.79</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>28.54</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>28.79</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>2633618.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>5152234.8</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>5152234.8</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>5772335.9</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>8563758.98</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>8563758.98</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>-663609.0332852043</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>2633618</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>2633618.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>28.66</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>28.52</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>28.77</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>28.52</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>28.77</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>2213338.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>5248524.8</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>5248524.8</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>5884237.2</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>8610119.16</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>8610119.16</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>-491000.5120926546</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>2213338</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>2213338.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>28.63</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>28.52</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>28.78</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>28.52</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>28.78</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>11898179.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>5884801.6</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>5884801.6</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>5874258.5</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>8681455.78</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>8681455.779999999</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>-181851.177814275</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>11898179</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>11898179.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,21 +16537,17 @@
           <t>28.53</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>28.52</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
+      <c r="AM38" t="n">
+        <v>28.52</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>28.78</v>
+      </c>
+      <c r="AO38" t="inlineStr">
         <is>
           <t>28.78</t>
         </is>
       </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>28.78</t>
-        </is>
-      </c>
       <c r="AP38" t="inlineStr">
         <is>
           <t>14.54</t>
@@ -16808,20 +16588,16 @@
           <t>6488238.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>4749451.2</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>4749451.2</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>4939269.8</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>8817616.86</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>8817616.859999999</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>-771376.122494651</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>6488238</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>6488238.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>28.68</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>28.59</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>28.79</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>28.59</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>28.79</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>2527801.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>6217139.2</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>6217139.2</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>4834769.4</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>8823050.78</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>8823050.779999999</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>-1006368.931948951</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>2527801</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>2527801.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,21 +17397,17 @@
           <t>28.66</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>28.64</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
+      <c r="AM40" t="n">
+        <v>28.64</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>28.78</v>
+      </c>
+      <c r="AO40" t="inlineStr">
         <is>
           <t>28.78</t>
         </is>
       </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>28.78</t>
-        </is>
-      </c>
       <c r="AP40" t="inlineStr">
         <is>
           <t>31.81</t>
@@ -17680,20 +17448,16 @@
           <t>3115068.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>6392437.0</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>6392437</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>4894234.9</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>8848475.32</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>8848475.32</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>-881798.6621712027</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>3115068</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>3115068.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,21 +17827,17 @@
           <t>28.58</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>28.64</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
+      <c r="AM41" t="n">
+        <v>28.64</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>28.77</v>
+      </c>
+      <c r="AO41" t="inlineStr">
         <is>
           <t>28.77</t>
         </is>
       </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>28.77</t>
-        </is>
-      </c>
       <c r="AP41" t="inlineStr">
         <is>
           <t>23.25</t>
@@ -18116,20 +17878,16 @@
           <t>5394722.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>6519949.6</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>6519949.6</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>5071311.2</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>8834063.72</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>8834063.720000001</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>-735269.7888397332</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>5394722</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>5394722.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,21 +18257,17 @@
           <t>28.48</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>28.63</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
+      <c r="AM42" t="n">
+        <v>28.63</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>28.76</v>
+      </c>
+      <c r="AO42" t="inlineStr">
         <is>
           <t>28.76</t>
         </is>
       </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>28.76</t>
-        </is>
-      </c>
       <c r="AP42" t="inlineStr">
         <is>
           <t>16.26</t>
@@ -18552,20 +18308,16 @@
           <t>6221427.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>5863715.4</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>5863715.4</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>5129783.2</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>8790589.08</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>8790589.08</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>-743931.8344790731</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>6221427</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>6221427.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,21 +18687,17 @@
           <t>28.41</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>28.65</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
+      <c r="AM43" t="n">
+        <v>28.65</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>28.74</v>
+      </c>
+      <c r="AO43" t="inlineStr">
         <is>
           <t>28.74</t>
         </is>
       </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>28.74</t>
-        </is>
-      </c>
       <c r="AP43" t="inlineStr">
         <is>
           <t>14.88</t>
@@ -18988,20 +18738,16 @@
           <t>13826678.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>5129088.4</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>5129088.4</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>4888140.0</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>8785320.84</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>8785320.84</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>-818312.7270181635</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>13826678</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>13826678.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,21 +19117,17 @@
           <t>28.26</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>28.62</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
+      <c r="AM44" t="n">
+        <v>28.62</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>28.72</v>
+      </c>
+      <c r="AO44" t="inlineStr">
         <is>
           <t>28.72</t>
         </is>
       </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>28.72</t>
-        </is>
-      </c>
       <c r="AP44" t="inlineStr">
         <is>
           <t>-24.80</t>
@@ -19424,20 +19168,16 @@
           <t>3404290.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>3452399.6</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>3452399.6</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>4041223.9</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>8683153.86</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>8683153.859999999</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>-1710194.011823357</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>3404290</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>3404290.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>28.24</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>28.61</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>28.72</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>28.61</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>28.72</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>3752631.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>3396032.8</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>3396032.8</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>4115249.1</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>8728203.1</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>8728203.1</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>-1806547.346837084</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>3752631</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>3752631.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
@@ -20057,7 +19793,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -20241,15 +19977,11 @@
           <t>21.83</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>21.89</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>21.86</t>
-        </is>
+      <c r="AM46" t="n">
+        <v>21.89</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>21.86</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
@@ -20296,20 +20028,16 @@
           <t>3923777.0</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>1771893.6</t>
-        </is>
+      <c r="AX46" t="n">
+        <v>1771893.6</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
           <t>1729816.3</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>1677601.62</t>
-        </is>
+      <c r="AZ46" t="n">
+        <v>1677601.62</v>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
@@ -20326,8 +20054,10 @@
           <t>46573.32550365617</t>
         </is>
       </c>
-      <c r="BD46" t="n">
-        <v>3923777</v>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>3923777.0</t>
+        </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
@@ -20493,7 +20223,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20677,15 +20407,11 @@
           <t>21.81</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>21.89</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>21.86</t>
-        </is>
+      <c r="AM47" t="n">
+        <v>21.89</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>21.86</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
@@ -20732,20 +20458,16 @@
           <t>913177.0</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>1118738.8</t>
-        </is>
+      <c r="AX47" t="n">
+        <v>1118738.8</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>1689309.7</t>
         </is>
       </c>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>1652530.6</t>
-        </is>
+      <c r="AZ47" t="n">
+        <v>1652530.6</v>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
@@ -20762,8 +20484,10 @@
           <t>-151379.9227839094</t>
         </is>
       </c>
-      <c r="BD47" t="n">
-        <v>913177</v>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>913177.0</t>
+        </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
@@ -20929,7 +20653,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -21113,15 +20837,11 @@
           <t>21.78</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>21.88</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>21.86</t>
-        </is>
+      <c r="AM48" t="n">
+        <v>21.88</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>21.86</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
@@ -21168,20 +20888,16 @@
           <t>2424359.0</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>1329829.6</t>
-        </is>
+      <c r="AX48" t="n">
+        <v>1329829.6</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
           <t>1826002.7</t>
         </is>
       </c>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>1658030.16</t>
-        </is>
+      <c r="AZ48" t="n">
+        <v>1658030.16</v>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
@@ -21198,8 +20914,10 @@
           <t>-106199.5659524344</t>
         </is>
       </c>
-      <c r="BD48" t="n">
-        <v>2424359</v>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>2424359.0</t>
+        </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
@@ -21365,7 +21083,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21549,15 +21267,11 @@
           <t>21.77</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>21.89</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>21.86</t>
-        </is>
+      <c r="AM49" t="n">
+        <v>21.89</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>21.86</v>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
@@ -21604,20 +21318,16 @@
           <t>852056.0</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>1291675.8</t>
-        </is>
+      <c r="AX49" t="n">
+        <v>1291675.8</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
           <t>1823764.4</t>
         </is>
       </c>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>1634806.12</t>
-        </is>
+      <c r="AZ49" t="n">
+        <v>1634806.12</v>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
@@ -21634,8 +21344,10 @@
           <t>-199775.7145520262</t>
         </is>
       </c>
-      <c r="BD49" t="n">
-        <v>852056</v>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>852056.0</t>
+        </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
@@ -21801,7 +21513,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21985,15 +21697,11 @@
           <t>21.78</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>21.89</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>21.86</t>
-        </is>
+      <c r="AM50" t="n">
+        <v>21.89</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>21.86</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
@@ -22040,20 +21748,16 @@
           <t>746099.0</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>1514317.4</t>
-        </is>
+      <c r="AX50" t="n">
+        <v>1514317.4</v>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
           <t>1902856.9</t>
         </is>
       </c>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>1649983.16</t>
-        </is>
+      <c r="AZ50" t="n">
+        <v>1649983.16</v>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
@@ -22070,8 +21774,10 @@
           <t>-157860.044174585</t>
         </is>
       </c>
-      <c r="BD50" t="n">
-        <v>746099</v>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>746099.0</t>
+        </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
@@ -22237,7 +21943,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -22421,15 +22127,11 @@
           <t>21.83</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>21.9</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>21.87</t>
-        </is>
+      <c r="AM51" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>21.87</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
@@ -22476,20 +22178,16 @@
           <t>658003.0</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>1687739.0</t>
-        </is>
+      <c r="AX51" t="n">
+        <v>1687739</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>2082449.9</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>1663241.0</t>
-        </is>
+      <c r="AZ51" t="n">
+        <v>1663241</v>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
@@ -22506,8 +22204,10 @@
           <t>-80990.12062914856</t>
         </is>
       </c>
-      <c r="BD51" t="n">
-        <v>658003</v>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>658003.0</t>
+        </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
@@ -22673,7 +22373,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -22857,15 +22557,11 @@
           <t>21.9</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>21.9</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>21.87</t>
-        </is>
+      <c r="AM52" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>21.87</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -22912,20 +22608,16 @@
           <t>1968631.0</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>2259880.6</t>
-        </is>
+      <c r="AX52" t="n">
+        <v>2259880.6</v>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
           <t>2544680.6</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>1727234.48</t>
-        </is>
+      <c r="AZ52" t="n">
+        <v>1727234.48</v>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
@@ -22942,8 +22634,10 @@
           <t>41155.4173153732</t>
         </is>
       </c>
-      <c r="BD52" t="n">
-        <v>1968631</v>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>1968631.0</t>
+        </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
@@ -23109,7 +22803,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23293,15 +22987,11 @@
           <t>21.92</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>21.91</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>21.88</t>
-        </is>
+      <c r="AM53" t="n">
+        <v>21.91</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>21.88</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -23348,20 +23038,16 @@
           <t>2233590.0</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>2322175.8</t>
-        </is>
+      <c r="AX53" t="n">
+        <v>2322175.8</v>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
           <t>2634363.1</t>
         </is>
       </c>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>1786149.68</t>
-        </is>
+      <c r="AZ53" t="n">
+        <v>1786149.68</v>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
@@ -23378,8 +23064,10 @@
           <t>73754.77804628387</t>
         </is>
       </c>
-      <c r="BD53" t="n">
-        <v>2233590</v>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>2233590.0</t>
+        </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
@@ -23545,7 +23233,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23729,15 +23417,11 @@
           <t>21.98</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>21.92</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>21.87</t>
-        </is>
+      <c r="AM54" t="n">
+        <v>21.92</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>21.87</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -23784,20 +23468,16 @@
           <t>1965264.0</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>2355853.0</t>
-        </is>
+      <c r="AX54" t="n">
+        <v>2355853</v>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>2548373.5</t>
         </is>
       </c>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>1784559.2</t>
-        </is>
+      <c r="AZ54" t="n">
+        <v>1784559.2</v>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
@@ -23814,8 +23494,10 @@
           <t>89302.72987450333</t>
         </is>
       </c>
-      <c r="BD54" t="n">
-        <v>1965264</v>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>1965264.0</t>
+        </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
@@ -23981,7 +23663,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -24165,15 +23847,11 @@
           <t>21.99</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>21.92</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>21.87</t>
-        </is>
+      <c r="AM55" t="n">
+        <v>21.92</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>21.87</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
@@ -24220,20 +23898,16 @@
           <t>1613207.0</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>2291396.4</t>
-        </is>
+      <c r="AX55" t="n">
+        <v>2291396.4</v>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
           <t>2468014.0</t>
         </is>
       </c>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>1771971.06</t>
-        </is>
+      <c r="AZ55" t="n">
+        <v>1771971.06</v>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
@@ -24250,8 +23924,10 @@
           <t>137073.9207050134</t>
         </is>
       </c>
-      <c r="BD55" t="n">
-        <v>1613207</v>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>1613207.0</t>
+        </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
@@ -24417,7 +24093,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -24601,15 +24277,11 @@
           <t>21.97</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>21.91</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>21.86</t>
-        </is>
+      <c r="AM56" t="n">
+        <v>21.91</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>21.86</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -24656,20 +24328,16 @@
           <t>3518711.0</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>2477160.8</t>
-        </is>
+      <c r="AX56" t="n">
+        <v>2477160.8</v>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
           <t>2557856.6</t>
         </is>
       </c>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>1777012.02</t>
-        </is>
+      <c r="AZ56" t="n">
+        <v>1777012.02</v>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
@@ -24686,8 +24354,10 @@
           <t>238143.37472342</t>
         </is>
       </c>
-      <c r="BD56" t="n">
-        <v>3518711</v>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>3518711.0</t>
+        </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
@@ -24853,7 +24523,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -25037,15 +24707,11 @@
           <t>52.72000000000001</t>
         </is>
       </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>52.61</t>
-        </is>
-      </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>52.42</t>
-        </is>
+      <c r="AM57" t="n">
+        <v>52.61</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>52.42</v>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
@@ -25092,20 +24758,16 @@
           <t>2606608.0</t>
         </is>
       </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>1852996.2</t>
-        </is>
+      <c r="AX57" t="n">
+        <v>1852996.2</v>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
           <t>1767055.1</t>
         </is>
       </c>
-      <c r="AZ57" t="inlineStr">
-        <is>
-          <t>1674391.68</t>
-        </is>
+      <c r="AZ57" t="n">
+        <v>1674391.68</v>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
@@ -25122,8 +24784,10 @@
           <t>50962.36429714784</t>
         </is>
       </c>
-      <c r="BD57" t="n">
-        <v>2606608</v>
+      <c r="BD57" t="inlineStr">
+        <is>
+          <t>2606608.0</t>
+        </is>
       </c>
       <c r="BE57" t="inlineStr">
         <is>
@@ -25289,7 +24953,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -25473,15 +25137,11 @@
           <t>52.58</t>
         </is>
       </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>52.56</t>
-        </is>
-      </c>
-      <c r="AN58" t="inlineStr">
-        <is>
-          <t>52.41</t>
-        </is>
+      <c r="AM58" t="n">
+        <v>52.56</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>52.41</v>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
@@ -25528,20 +25188,16 @@
           <t>2350282.0</t>
         </is>
       </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>1511336.0</t>
-        </is>
+      <c r="AX58" t="n">
+        <v>1511336</v>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
           <t>1711841.7</t>
         </is>
       </c>
-      <c r="AZ58" t="inlineStr">
-        <is>
-          <t>1661952.44</t>
-        </is>
+      <c r="AZ58" t="n">
+        <v>1661952.44</v>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
@@ -25558,8 +25214,10 @@
           <t>-12256.12165606418</t>
         </is>
       </c>
-      <c r="BD58" t="n">
-        <v>2350282</v>
+      <c r="BD58" t="inlineStr">
+        <is>
+          <t>2350282.0</t>
+        </is>
       </c>
       <c r="BE58" t="inlineStr">
         <is>
@@ -25725,7 +25383,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -25909,15 +25567,11 @@
           <t>52.48</t>
         </is>
       </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>52.54</t>
-        </is>
-      </c>
-      <c r="AN59" t="inlineStr">
-        <is>
-          <t>52.41</t>
-        </is>
+      <c r="AM59" t="n">
+        <v>52.54</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>52.41</v>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
@@ -25964,20 +25618,16 @@
           <t>1266362.0</t>
         </is>
       </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>1440104.0</t>
-        </is>
+      <c r="AX59" t="n">
+        <v>1440104</v>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
           <t>1725040.4</t>
         </is>
       </c>
-      <c r="AZ59" t="inlineStr">
-        <is>
-          <t>1651135.98</t>
-        </is>
+      <c r="AZ59" t="n">
+        <v>1651135.98</v>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
@@ -25994,8 +25644,10 @@
           <t>-74667.02581579308</t>
         </is>
       </c>
-      <c r="BD59" t="n">
-        <v>1266362</v>
+      <c r="BD59" t="inlineStr">
+        <is>
+          <t>1266362.0</t>
+        </is>
       </c>
       <c r="BE59" t="inlineStr">
         <is>
@@ -26161,7 +25813,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -26345,15 +25997,11 @@
           <t>52.36</t>
         </is>
       </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>52.52</t>
-        </is>
-      </c>
-      <c r="AN60" t="inlineStr">
-        <is>
-          <t>52.41</t>
-        </is>
+      <c r="AM60" t="n">
+        <v>52.52</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>52.41</v>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
@@ -26400,20 +26048,16 @@
           <t>2130158.0</t>
         </is>
       </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>1825993.2</t>
-        </is>
+      <c r="AX60" t="n">
+        <v>1825993.2</v>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
           <t>1656853.3</t>
         </is>
       </c>
-      <c r="AZ60" t="inlineStr">
-        <is>
-          <t>1652441.76</t>
-        </is>
+      <c r="AZ60" t="n">
+        <v>1652441.76</v>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
@@ -26430,8 +26074,10 @@
           <t>-45024.49512198474</t>
         </is>
       </c>
-      <c r="BD60" t="n">
-        <v>2130158</v>
+      <c r="BD60" t="inlineStr">
+        <is>
+          <t>2130158.0</t>
+        </is>
       </c>
       <c r="BE60" t="inlineStr">
         <is>
@@ -26597,7 +26243,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -26781,15 +26427,11 @@
           <t>52.42</t>
         </is>
       </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>52.54</t>
-        </is>
-      </c>
-      <c r="AN61" t="inlineStr">
-        <is>
-          <t>52.42</t>
-        </is>
+      <c r="AM61" t="n">
+        <v>52.54</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>52.42</v>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
@@ -26836,20 +26478,16 @@
           <t>911571.0</t>
         </is>
       </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>1749477.2</t>
-        </is>
+      <c r="AX61" t="n">
+        <v>1749477.2</v>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
           <t>1753075.3</t>
         </is>
       </c>
-      <c r="AZ61" t="inlineStr">
-        <is>
-          <t>1643897.26</t>
-        </is>
+      <c r="AZ61" t="n">
+        <v>1643897.26</v>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
@@ -26866,8 +26504,10 @@
           <t>-93619.57644790178</t>
         </is>
       </c>
-      <c r="BD61" t="n">
-        <v>911571</v>
+      <c r="BD61" t="inlineStr">
+        <is>
+          <t>911571.0</t>
+        </is>
       </c>
       <c r="BE61" t="inlineStr">
         <is>
@@ -27033,7 +26673,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -27217,15 +26857,11 @@
           <t>52.5</t>
         </is>
       </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>52.54</t>
-        </is>
-      </c>
-      <c r="AN62" t="inlineStr">
-        <is>
-          <t>52.42</t>
-        </is>
+      <c r="AM62" t="n">
+        <v>52.54</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>52.42</v>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
@@ -27272,20 +26908,16 @@
           <t>898307.0</t>
         </is>
       </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>1681114.0</t>
-        </is>
+      <c r="AX62" t="n">
+        <v>1681114</v>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
           <t>1838819.0</t>
         </is>
       </c>
-      <c r="AZ62" t="inlineStr">
-        <is>
-          <t>1648985.96</t>
-        </is>
+      <c r="AZ62" t="n">
+        <v>1648985.96</v>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
@@ -27302,8 +26934,10 @@
           <t>-29134.67204035819</t>
         </is>
       </c>
-      <c r="BD62" t="n">
-        <v>898307</v>
+      <c r="BD62" t="inlineStr">
+        <is>
+          <t>898307.0</t>
+        </is>
       </c>
       <c r="BE62" t="inlineStr">
         <is>
@@ -27469,7 +27103,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -27653,15 +27287,11 @@
           <t>52.64</t>
         </is>
       </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>52.53</t>
-        </is>
-      </c>
-      <c r="AN63" t="inlineStr">
-        <is>
-          <t>52.42</t>
-        </is>
+      <c r="AM63" t="n">
+        <v>52.53</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>52.42</v>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
@@ -27708,20 +27338,16 @@
           <t>1994122.0</t>
         </is>
       </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>1912347.4</t>
-        </is>
+      <c r="AX63" t="n">
+        <v>1912347.4</v>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
           <t>2238228.3</t>
         </is>
       </c>
-      <c r="AZ63" t="inlineStr">
-        <is>
-          <t>1663391.0</t>
-        </is>
+      <c r="AZ63" t="n">
+        <v>1663391</v>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
@@ -27738,8 +27364,10 @@
           <t>65448.28682900267</t>
         </is>
       </c>
-      <c r="BD63" t="n">
-        <v>1994122</v>
+      <c r="BD63" t="inlineStr">
+        <is>
+          <t>1994122.0</t>
+        </is>
       </c>
       <c r="BE63" t="inlineStr">
         <is>
@@ -27905,7 +27533,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -28089,15 +27717,11 @@
           <t>52.77999999999999</t>
         </is>
       </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>52.52</t>
-        </is>
-      </c>
-      <c r="AN64" t="inlineStr">
-        <is>
-          <t>52.43</t>
-        </is>
+      <c r="AM64" t="n">
+        <v>52.52</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>52.43</v>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
@@ -28144,20 +27768,16 @@
           <t>3195808.0</t>
         </is>
       </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>2009976.8</t>
-        </is>
+      <c r="AX64" t="n">
+        <v>2009976.8</v>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
           <t>2157042.3</t>
         </is>
       </c>
-      <c r="AZ64" t="inlineStr">
-        <is>
-          <t>1640429.16</t>
-        </is>
+      <c r="AZ64" t="n">
+        <v>1640429.16</v>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
@@ -28174,8 +27794,10 @@
           <t>80820.6106841967</t>
         </is>
       </c>
-      <c r="BD64" t="n">
-        <v>3195808</v>
+      <c r="BD64" t="inlineStr">
+        <is>
+          <t>3195808.0</t>
+        </is>
       </c>
       <c r="BE64" t="inlineStr">
         <is>
@@ -28341,7 +27963,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -28525,15 +28147,11 @@
           <t>52.94</t>
         </is>
       </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>52.54</t>
-        </is>
-      </c>
-      <c r="AN65" t="inlineStr">
-        <is>
-          <t>52.44</t>
-        </is>
+      <c r="AM65" t="n">
+        <v>52.54</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>52.44</v>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
@@ -28580,20 +28198,16 @@
           <t>1747578.0</t>
         </is>
       </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>1487713.4</t>
-        </is>
+      <c r="AX65" t="n">
+        <v>1487713.4</v>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
           <t>2093044.6</t>
         </is>
       </c>
-      <c r="AZ65" t="inlineStr">
-        <is>
-          <t>1594015.84</t>
-        </is>
+      <c r="AZ65" t="n">
+        <v>1594015.84</v>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
@@ -28610,8 +28224,10 @@
           <t>-28857.44847567612</t>
         </is>
       </c>
-      <c r="BD65" t="n">
-        <v>1747578</v>
+      <c r="BD65" t="inlineStr">
+        <is>
+          <t>1747578.0</t>
+        </is>
       </c>
       <c r="BE65" t="inlineStr">
         <is>
@@ -28777,7 +28393,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -28961,15 +28577,11 @@
           <t>52.94000000000001</t>
         </is>
       </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>52.52</t>
-        </is>
-      </c>
-      <c r="AN66" t="inlineStr">
-        <is>
-          <t>52.43</t>
-        </is>
+      <c r="AM66" t="n">
+        <v>52.52</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>52.43</v>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
@@ -29016,20 +28628,16 @@
           <t>569755.0</t>
         </is>
       </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>1756673.4</t>
-        </is>
+      <c r="AX66" t="n">
+        <v>1756673.4</v>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
           <t>2074638.1</t>
         </is>
       </c>
-      <c r="AZ66" t="inlineStr">
-        <is>
-          <t>1598199.14</t>
-        </is>
+      <c r="AZ66" t="n">
+        <v>1598199.14</v>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
@@ -29046,8 +28654,10 @@
           <t>-29342.2669727914</t>
         </is>
       </c>
-      <c r="BD66" t="n">
-        <v>569755</v>
+      <c r="BD66" t="inlineStr">
+        <is>
+          <t>569755.0</t>
+        </is>
       </c>
       <c r="BE66" t="inlineStr">
         <is>
@@ -29213,7 +28823,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -29397,15 +29007,11 @@
           <t>52.96</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>52.48</t>
-        </is>
-      </c>
-      <c r="AN67" t="inlineStr">
-        <is>
-          <t>52.42</t>
-        </is>
+      <c r="AM67" t="n">
+        <v>52.48</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>52.42</v>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
@@ -29452,20 +29058,16 @@
           <t>2054474.0</t>
         </is>
       </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>1996524.0</t>
-        </is>
+      <c r="AX67" t="n">
+        <v>1996524</v>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
           <t>2142934.5</t>
         </is>
       </c>
-      <c r="AZ67" t="inlineStr">
-        <is>
-          <t>1619353.92</t>
-        </is>
+      <c r="AZ67" t="n">
+        <v>1619353.92</v>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
@@ -29482,8 +29084,10 @@
           <t>97208.39470892912</t>
         </is>
       </c>
-      <c r="BD67" t="n">
-        <v>2054474</v>
+      <c r="BD67" t="inlineStr">
+        <is>
+          <t>2054474.0</t>
+        </is>
       </c>
       <c r="BE67" t="inlineStr">
         <is>
